--- a/etf_holdings/2026-10-20_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-20_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:30</t>
+          <t>2026-10-20 21:42:12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0%2420</t>
+          <t>-0.62%2405</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2420</v>
+        <v>2405</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7.87%1,544,000</t>
+          <t>7.95%1,544,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.87%</t>
+          <t>7.95%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:30</t>
+          <t>2026-10-20 21:42:12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,33 +570,33 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-1.06%4205</t>
+          <t>-1.31%4150</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4205</v>
+        <v>4150</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.59%736,000</t>
+          <t>7.03%786,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.59%</t>
+          <t>7.03%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>736000</v>
+        <v>786000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:30</t>
+          <t>2026-10-20 21:42:12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-3.79%482</t>
+          <t>-1.45%475</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-3.79%</t>
+          <t>-1.45%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.02%5,709,000</t>
+          <t>5.85%5,709,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.02%</t>
+          <t>5.85%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:30</t>
+          <t>2026-10-20 21:42:12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-2.07%663</t>
+          <t>-2.56%646</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>-2.56%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>663</v>
+        <v>646</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.34%3,745,000</t>
+          <t>5.28%3,745,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.34%</t>
+          <t>5.28%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:30</t>
+          <t>2026-10-20 21:42:12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+2.17%1885</t>
+          <t>+2.12%1925</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1885</v>
+        <v>1925</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.95%1,016,225</t>
+          <t>4.08%1,016,225</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.95%</t>
+          <t>4.08%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:30</t>
+          <t>2026-10-20 21:42:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-6.92%821</t>
+          <t>-2.56%800</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-6.92%</t>
+          <t>-2.56%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>821</v>
+        <v>800</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.92%2,110,000</t>
+          <t>3.69%2,110,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.92%</t>
+          <t>3.69%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:30</t>
+          <t>2026-10-20 21:42:12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,12 +875,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-1.8%547</t>
+          <t>0%547</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -888,12 +888,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.70%3,158,000</t>
+          <t>3.68%3,158,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>3.68%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:30</t>
+          <t>2026-10-20 21:42:12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3491昇達科</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-4.81%1385</t>
+          <t>-0.25%2000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-4.81%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1385</v>
+        <v>2000</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.62%1,180,000</t>
+          <t>3.63%851,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>3.63%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1180000</v>
+        <v>851000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:30</t>
+          <t>2026-10-20 21:42:12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+0.25%2005</t>
+          <t>-3.97%1330</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-3.97%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2005</v>
+        <v>1330</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.56%845,000</t>
+          <t>3.48%1,180,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>3.48%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>845000</v>
+        <v>1180000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:30</t>
+          <t>2026-10-20 21:42:12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.42%6245</t>
+          <t>-3.51%4945</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>6245</v>
+        <v>4945</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.38%251,000</t>
+          <t>3.37%309,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>3.37%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>251000</v>
+        <v>309000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:30</t>
+          <t>2026-10-20 21:42:12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,25 +1114,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.77%5125</t>
+          <t>-4.32%5975</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>-4.32%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5125</v>
+        <v>5975</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.36%309,000</t>
+          <t>3.36%253,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1141,11 +1141,11 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>309000</v>
+        <v>253000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:30</t>
+          <t>2026-10-20 21:42:12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.58%5235</t>
+          <t>-6.4%4900</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5235</v>
+        <v>4900</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.30%301,000</t>
+          <t>3.35%301,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:30</t>
+          <t>2026-10-20 21:42:12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.35%9920</t>
+          <t>+1.81%10100</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>+1.81%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>9920</v>
+        <v>10100</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.70%129,000</t>
+          <t>2.72%129,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.72%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:30</t>
+          <t>2026-10-20 21:42:12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+0.15%3320</t>
+          <t>+0.15%3325</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1311,20 +1311,20 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>3320</v>
+        <v>3325</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.60%372,000</t>
+          <t>2.64%374,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>2.64%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>372000</v>
+        <v>374000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:30</t>
+          <t>2026-10-20 21:42:12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,20 +1363,20 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-2.22%882</t>
+          <t>-4.31%844</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>-4.31%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>882</v>
+        <v>844</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.05%1,082,000</t>
+          <t>2.05%1,091,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1385,11 +1385,11 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1082000</v>
+        <v>1091000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:31</t>
+          <t>2026-10-20 21:42:13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3265台星科</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-6.69%251</t>
+          <t>-0.76%262</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-6.69%</t>
+          <t>-0.76%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.89%3,345,000</t>
+          <t>1.82%3,234,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>3345000</v>
+        <v>3234000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:31</t>
+          <t>2026-10-20 21:42:13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>3265台星科</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.19%264</t>
+          <t>-1.2%248</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.79%3,216,000</t>
+          <t>1.80%3,364,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.80%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>3216000</v>
+        <v>3364000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:31</t>
+          <t>2026-10-20 21:42:13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,33 +1546,33 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.3%491.5</t>
+          <t>-1.22%485.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>491.5</v>
+        <v>485.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.59%1,529,000</t>
+          <t>1.61%1,539,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1529000</v>
+        <v>1539000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:31</t>
+          <t>2026-10-20 21:42:13</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,33 +1607,33 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-0.9%767</t>
+          <t>-2.35%749</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-2.35%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>767</v>
+        <v>749</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.53%940,000</t>
+          <t>1.54%942,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>940000</v>
+        <v>942000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:31</t>
+          <t>2026-10-20 21:42:13</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6672騰輝電子-KY</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-4.91%562</t>
+          <t>-4.91%1550</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1677,11 +1677,11 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>562</v>
+        <v>1550</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.46%1,173,000</t>
+          <t>1.46%421,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1173000</v>
+        <v>421000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:31</t>
+          <t>2026-10-20 21:42:13</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,25 +1724,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5483中美晶</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-3.25%193.5</t>
+          <t>-3.42%127</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-3.25%</t>
+          <t>-3.42%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>193.5</v>
+        <v>127</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.44%3,415,000</t>
+          <t>1.44%5,153,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>3415000</v>
+        <v>5153000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:31</t>
+          <t>2026-10-20 21:42:13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>6214精誠</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-1.13%131.5</t>
+          <t>0%196.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>131.5</v>
+        <v>196.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.43%5,116,000</t>
+          <t>1.44%3,438,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.44%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>5116000</v>
+        <v>3438000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:31</t>
+          <t>2026-10-20 21:42:13</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,34 +1846,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6214精誠</t>
+          <t>5483中美晶</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-0.51%196.5</t>
+          <t>-1.03%191.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>196.5</v>
+        <v>191.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.43%3,438,000</t>
+          <t>1.42%3,439,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>3438000</v>
+        <v>3439000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:31</t>
+          <t>2026-10-20 21:42:13</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>6672騰輝電子-KY</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+0.93%1630</t>
+          <t>+1.42%570</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+0.93%</t>
+          <t>+1.42%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1630</v>
+        <v>570</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.42%418,000</t>
+          <t>1.40%1,175,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>418000</v>
+        <v>1175000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:31</t>
+          <t>2026-10-20 21:42:13</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-1.37%180</t>
+          <t>+5%189</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>+5%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.40%3,638,000</t>
+          <t>1.39%3,638,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:31</t>
+          <t>2026-10-20 21:42:13</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-0.88%679</t>
+          <t>+0.74%684</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+0.74%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:31</t>
+          <t>2026-10-20 21:42:13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,20 +2095,20 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-1.54%352</t>
+          <t>+0.85%355</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-1.54%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.31%1,737,000</t>
+          <t>1.31%1,751,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2117,11 +2117,11 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>1737000</v>
+        <v>1751000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:31</t>
+          <t>2026-10-20 21:42:13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,25 +2151,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.87%1525</t>
+          <t>-1.49%660</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.87%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1525</v>
+        <v>660</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.26%382,000</t>
+          <t>1.26%883,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2178,11 +2178,11 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>382000</v>
+        <v>883000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:31</t>
+          <t>2026-10-20 21:42:13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,20 +2217,20 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-1.91%256.5</t>
+          <t>-2.14%251</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>-2.14%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>256.5</v>
+        <v>251</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.25%2,268,000</t>
+          <t>1.25%2,287,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2239,11 +2239,11 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>2268000</v>
+        <v>2287000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:31</t>
+          <t>2026-10-20 21:42:13</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,25 +2273,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>5425台半</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-3.03%15980</t>
+          <t>-0.98%90.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-3.03%</t>
+          <t>-0.98%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>15980</v>
+        <v>90.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.25%35,900</t>
+          <t>1.25%6,406,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2300,11 +2300,11 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>35900</v>
+        <v>6406000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:33</t>
+          <t>2026-10-20 21:42:15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,25 +2334,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>5425台半</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.3%91.4</t>
+          <t>+1.31%1545</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>91.40000000000001</v>
+        <v>1545</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.24%6,382,000</t>
+          <t>1.24%382,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2361,11 +2361,11 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>6382000</v>
+        <v>382000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:33</t>
+          <t>2026-10-20 21:42:15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-0.15%670</t>
+          <t>-0.5%15900</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>670</v>
+        <v>15900</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.24%876,000</t>
+          <t>1.22%35,900</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>876000</v>
+        <v>35900</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:33</t>
+          <t>2026-10-20 21:42:15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2478大毅</t>
+          <t>3090日電貿</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-8.27%122</t>
+          <t>-3.38%157</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-8.27%</t>
+          <t>-3.38%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.21%4,331,000</t>
+          <t>1.13%3,280,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>4331000</v>
+        <v>3280000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:33</t>
+          <t>2026-10-20 21:42:15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3090日電貿</t>
+          <t>2478大毅</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-4.69%162.5</t>
+          <t>-1.64%120</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-4.69%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>162.5</v>
+        <v>120</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.18%3,280,000</t>
+          <t>1.13%4,364,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>3280000</v>
+        <v>4364000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:33</t>
+          <t>2026-10-20 21:42:15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,25 +2583,25 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-4.01%263</t>
+          <t>-2.66%256</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-4.01%</t>
+          <t>-2.66%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.10%1,910,000</t>
+          <t>1.07%1,910,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:33</t>
+          <t>2026-10-20 21:42:15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,25 +2644,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-2.61%634</t>
+          <t>-3.15%614</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-2.61%</t>
+          <t>-3.15%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>634</v>
+        <v>614</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.08%790,000</t>
+          <t>1.07%790,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:33</t>
+          <t>2026-10-20 21:42:15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-3.35%491</t>
+          <t>-1.63%483</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-3.35%</t>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.07%1,000,000</t>
+          <t>1.04%1,000,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.04%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:33</t>
+          <t>2026-10-20 21:42:15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,25 +2766,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-3.06%412.5</t>
+          <t>+0.12%413</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-3.06%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>412.5</v>
+        <v>413</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.92%1,032,000</t>
+          <t>0.91%1,032,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:33</t>
+          <t>2026-10-20 21:42:15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-3.5%827</t>
+          <t>-2.06%810</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-2.06%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>827</v>
+        <v>810</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.82%455,000</t>
+          <t>0.80%455,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.80%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:33</t>
+          <t>2026-10-20 21:42:15</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-1.16%213.5</t>
+          <t>-2.58%208</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>-2.58%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>213.5</v>
+        <v>208</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:33</t>
+          <t>2026-10-20 21:42:15</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,20 +2949,20 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-1.92%51.2</t>
+          <t>-2.15%50.1</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-1.92%</t>
+          <t>-2.15%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>51.2</v>
+        <v>50.1</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.47%4,312,000</t>
+          <t>0.47%4,343,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>4312000</v>
+        <v>4343000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:33</t>
+          <t>2026-10-20 21:42:15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,20 +3010,20 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.81%598</t>
+          <t>-0.84%593</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.81%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.39%304,000</t>
+          <t>0.39%306,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3032,11 +3032,11 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>304000</v>
+        <v>306000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:33</t>
+          <t>2026-10-20 21:42:15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,20 +3071,20 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-2.08%259</t>
+          <t>-2.9%251.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-2.08%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>259</v>
+        <v>251.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.35%627,000</t>
+          <t>0.35%632,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>627000</v>
+        <v>632000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:33</t>
+          <t>2026-10-20 21:42:15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-1.24%159.5</t>
+          <t>+3.13%164.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>+3.13%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>159.5</v>
+        <v>164.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:33</t>
+          <t>2026-10-20 21:42:15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,25 +3188,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2885元大金</t>
+          <t>2476鉅祥</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.65%71.7</t>
+          <t>-2.02%121.5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-1.65%</t>
+          <t>-2.02%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>71.7</v>
+        <v>121.5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.34%2,213,556</t>
+          <t>0.34%1,291,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>2213556</v>
+        <v>1291000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:34</t>
+          <t>2026-10-20 21:42:16</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,38 +3249,38 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2476鉅祥</t>
+          <t>2885元大金</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+0.4%124</t>
+          <t>-1.67%70.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+0.4%</t>
+          <t>-1.67%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>124</v>
+        <v>70.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.33%1,281,000</t>
+          <t>0.34%2,213,556</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>1281000</v>
+        <v>2213556</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:34</t>
+          <t>2026-10-20 21:42:16</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,25 +3315,25 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-2.96%985</t>
+          <t>-4.47%941</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-2.96%</t>
+          <t>-4.47%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>985</v>
+        <v>941</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.31%143,000</t>
+          <t>0.30%143,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:34</t>
+          <t>2026-10-20 21:42:16</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,25 +3376,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-5.62%1175</t>
+          <t>-1.7%1155</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-5.62%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1175</v>
+        <v>1155</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.11%42,000</t>
+          <t>0.10%42,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:34</t>
+          <t>2026-10-20 21:42:16</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-1.63%45.2</t>
+          <t>+0.33%45.35</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>45.2</v>
+        <v>45.35</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:34</t>
+          <t>2026-10-20 21:42:16</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+4.68%7830</t>
+          <t>-1.09%7745</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+4.68%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>7830</v>
+        <v>7745</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:34</t>
+          <t>2026-10-20 21:42:16</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3559,16 +3559,16 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-2%2695</t>
+          <t>-1.48%2655</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2695</v>
+        <v>2655</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:34</t>
+          <t>2026-10-20 21:42:16</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3620,16 +3620,16 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-2.69%163</t>
+          <t>+1.23%165</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-2.69%</t>
+          <t>+1.23%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:34</t>
+          <t>2026-10-20 21:42:16</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3676,25 +3676,25 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1519華城</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-1.83%644</t>
+          <t>-3%469.5</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-1.83%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>644</v>
+        <v>469.5</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>&lt;0.01%660</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>660</v>
+        <v>1000</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:34</t>
+          <t>2026-10-20 21:42:16</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3737,25 +3737,25 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>1519華城</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>+2.54%484</t>
+          <t>-2.02%631</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>+2.54%</t>
+          <t>-2.02%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>484</v>
+        <v>631</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%660</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3764,11 +3764,11 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>1000</v>
+        <v>660</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:34</t>
+          <t>2026-10-20 21:42:16</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3803,16 +3803,16 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>+0.37%53.9</t>
+          <t>-1.3%53.2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>53.9</v>
+        <v>53.2</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:34</t>
+          <t>2026-10-20 21:42:16</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3864,16 +3864,16 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-1.86%158.5</t>
+          <t>-3.15%153.5</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-1.86%</t>
+          <t>-3.15%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>158.5</v>
+        <v>153.5</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-20_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-20_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:12</t>
+          <t>2026-10-20 22:18:55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:12</t>
+          <t>2026-10-20 22:18:55</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:12</t>
+          <t>2026-10-20 22:18:55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:12</t>
+          <t>2026-10-20 22:18:55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:12</t>
+          <t>2026-10-20 22:18:55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:12</t>
+          <t>2026-10-20 22:18:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:12</t>
+          <t>2026-10-20 22:18:55</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:12</t>
+          <t>2026-10-20 22:18:55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:12</t>
+          <t>2026-10-20 22:18:55</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:12</t>
+          <t>2026-10-20 22:18:55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:12</t>
+          <t>2026-10-20 22:18:55</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:12</t>
+          <t>2026-10-20 22:18:55</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:12</t>
+          <t>2026-10-20 22:18:55</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:12</t>
+          <t>2026-10-20 22:18:55</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:12</t>
+          <t>2026-10-20 22:18:55</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:13</t>
+          <t>2026-10-20 22:18:56</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:13</t>
+          <t>2026-10-20 22:18:56</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:13</t>
+          <t>2026-10-20 22:18:56</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:13</t>
+          <t>2026-10-20 22:18:56</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:13</t>
+          <t>2026-10-20 22:18:56</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:13</t>
+          <t>2026-10-20 22:18:56</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:13</t>
+          <t>2026-10-20 22:18:56</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:13</t>
+          <t>2026-10-20 22:18:56</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:13</t>
+          <t>2026-10-20 22:18:56</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:13</t>
+          <t>2026-10-20 22:18:56</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:13</t>
+          <t>2026-10-20 22:18:56</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:13</t>
+          <t>2026-10-20 22:18:56</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:13</t>
+          <t>2026-10-20 22:18:56</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:13</t>
+          <t>2026-10-20 22:18:56</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:13</t>
+          <t>2026-10-20 22:18:56</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:15</t>
+          <t>2026-10-20 22:18:58</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:15</t>
+          <t>2026-10-20 22:18:58</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:15</t>
+          <t>2026-10-20 22:18:58</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:15</t>
+          <t>2026-10-20 22:18:58</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:15</t>
+          <t>2026-10-20 22:18:58</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:15</t>
+          <t>2026-10-20 22:18:58</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:15</t>
+          <t>2026-10-20 22:18:58</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:15</t>
+          <t>2026-10-20 22:18:58</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:15</t>
+          <t>2026-10-20 22:18:58</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:15</t>
+          <t>2026-10-20 22:18:58</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:15</t>
+          <t>2026-10-20 22:18:58</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:15</t>
+          <t>2026-10-20 22:18:58</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:15</t>
+          <t>2026-10-20 22:18:58</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:15</t>
+          <t>2026-10-20 22:18:58</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:15</t>
+          <t>2026-10-20 22:18:58</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:16</t>
+          <t>2026-10-20 22:18:59</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:16</t>
+          <t>2026-10-20 22:18:59</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:16</t>
+          <t>2026-10-20 22:18:59</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:16</t>
+          <t>2026-10-20 22:18:59</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:16</t>
+          <t>2026-10-20 22:18:59</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:16</t>
+          <t>2026-10-20 22:18:59</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:16</t>
+          <t>2026-10-20 22:18:59</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:16</t>
+          <t>2026-10-20 22:18:59</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:16</t>
+          <t>2026-10-20 22:18:59</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:16</t>
+          <t>2026-10-20 22:18:59</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:16</t>
+          <t>2026-10-20 22:18:59</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
